--- a/artfynd/A 23232-2026 artfynd.xlsx
+++ b/artfynd/A 23232-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121569815</v>
+        <v>121569805</v>
       </c>
       <c r="B2" t="n">
-        <v>91086</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>644289</v>
+        <v>644388</v>
       </c>
       <c r="R2" t="n">
-        <v>7170389</v>
+        <v>7170476</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121569818</v>
+        <v>121569808</v>
       </c>
       <c r="B3" t="n">
-        <v>90742</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>644292</v>
+        <v>644386</v>
       </c>
       <c r="R3" t="n">
-        <v>7170383</v>
+        <v>7170470</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569812</v>
+        <v>121569819</v>
       </c>
       <c r="B4" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>644277</v>
+        <v>644292</v>
       </c>
       <c r="R4" t="n">
-        <v>7170388</v>
+        <v>7170383</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569808</v>
+        <v>121569809</v>
       </c>
       <c r="B5" t="n">
-        <v>91028</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>644386</v>
+        <v>644348</v>
       </c>
       <c r="R5" t="n">
-        <v>7170470</v>
+        <v>7170471</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569810</v>
+        <v>121569806</v>
       </c>
       <c r="B6" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>644336</v>
+        <v>644388</v>
       </c>
       <c r="R6" t="n">
-        <v>7170459</v>
+        <v>7170476</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569813</v>
+        <v>121569807</v>
       </c>
       <c r="B7" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>644282</v>
+        <v>644386</v>
       </c>
       <c r="R7" t="n">
-        <v>7170379</v>
+        <v>7170470</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569805</v>
+        <v>121569818</v>
       </c>
       <c r="B8" t="n">
-        <v>91028</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>644388</v>
+        <v>644292</v>
       </c>
       <c r="R8" t="n">
-        <v>7170476</v>
+        <v>7170383</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1389,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569817</v>
+        <v>121569815</v>
       </c>
       <c r="B9" t="n">
-        <v>90577</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6020</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>644292</v>
+        <v>644289</v>
       </c>
       <c r="R9" t="n">
-        <v>7170383</v>
+        <v>7170389</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569807</v>
+        <v>121569817</v>
       </c>
       <c r="B10" t="n">
-        <v>90742</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6020</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>644386</v>
+        <v>644292</v>
       </c>
       <c r="R10" t="n">
-        <v>7170470</v>
+        <v>7170383</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569819</v>
+        <v>121569804</v>
       </c>
       <c r="B11" t="n">
-        <v>91028</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>644292</v>
+        <v>644340</v>
       </c>
       <c r="R11" t="n">
-        <v>7170383</v>
+        <v>7170520</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121569814</v>
+        <v>121569810</v>
       </c>
       <c r="B12" t="n">
-        <v>79710</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>644282</v>
+        <v>644336</v>
       </c>
       <c r="R12" t="n">
-        <v>7170385</v>
+        <v>7170459</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1800,16 +1745,11 @@
         <v>121569811</v>
       </c>
       <c r="B13" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1899,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121569809</v>
+        <v>121569812</v>
       </c>
       <c r="B14" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>644348</v>
+        <v>644277</v>
       </c>
       <c r="R14" t="n">
-        <v>7170471</v>
+        <v>7170388</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2001,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121569804</v>
+        <v>121569814</v>
       </c>
       <c r="B15" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>644340</v>
+        <v>644282</v>
       </c>
       <c r="R15" t="n">
-        <v>7170520</v>
+        <v>7170385</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2103,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121569806</v>
+        <v>121569813</v>
       </c>
       <c r="B16" t="n">
-        <v>90742</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>644388</v>
+        <v>644282</v>
       </c>
       <c r="R16" t="n">
-        <v>7170476</v>
+        <v>7170379</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2202,6 +2127,98 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121569816</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92285</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6331024</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Skeletocutis delicata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Miettinen &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fäboliden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>644295</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7170382</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23232-2026 artfynd.xlsx
+++ b/artfynd/A 23232-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569805</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569808</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569819</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569809</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569806</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569807</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569818</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569815</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569817</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569804</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569810</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569811</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569812</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569814</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569813</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2219,8 +2299,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569816</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>